--- a/data/trans_camb/P19C05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,3</t>
+          <t>-2,85; 2,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,29</t>
+          <t>-2,05; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,69</t>
+          <t>-4,04; 1,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,53</t>
+          <t>-0,4; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,35</t>
+          <t>-1,33; 3,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,27</t>
+          <t>-2,7; 2,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,6</t>
+          <t>-0,87; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,48</t>
+          <t>-1,04; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,05</t>
+          <t>-2,86; 0,99</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 128,51</t>
+          <t>-60,8; 126,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 174,73</t>
+          <t>-48,03; 167,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,51; 146,87</t>
+          <t>-98,3; 123,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 391,31</t>
+          <t>-21,0; 417,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 327,44</t>
+          <t>-44,77; 256,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,17; 277,34</t>
+          <t>-98,01; 231,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 142,57</t>
+          <t>-26,37; 131,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 126,97</t>
+          <t>-33,18; 124,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,07; 89,55</t>
+          <t>-89,27; 60,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,36</t>
+          <t>-2,15; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,48</t>
+          <t>-1,42; 3,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,76</t>
+          <t>-1,53; 4,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,91</t>
+          <t>-0,12; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,9</t>
+          <t>-2,39; 1,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,53</t>
+          <t>-2,6; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,78</t>
+          <t>-0,46; 2,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,15</t>
+          <t>-1,31; 2,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,48</t>
+          <t>-1,36; 2,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 110,24</t>
+          <t>-46,08; 105,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 146,13</t>
+          <t>-33,65; 164,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 151,78</t>
+          <t>-42,45; 171,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 183,98</t>
+          <t>-5,13; 186,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 70,99</t>
+          <t>-50,98; 72,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 94,51</t>
+          <t>-56,5; 90,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 94,3</t>
+          <t>-10,02; 111,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 79,89</t>
+          <t>-30,82; 78,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 89,18</t>
+          <t>-34,68; 83,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,52</t>
+          <t>-2,37; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,32</t>
+          <t>-5,09; 0,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,18</t>
+          <t>-5,6; 0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,87</t>
+          <t>-4,22; 1,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,56</t>
+          <t>-4,83; 1,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -1,43</t>
+          <t>-6,77; -1,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,2</t>
+          <t>-2,26; 2,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,09</t>
+          <t>-4,39; -0,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -1,46</t>
+          <t>-5,43; -1,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 87,22</t>
+          <t>-29,47; 87,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 11,41</t>
+          <t>-64,04; 14,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 6,42</t>
+          <t>-66,09; 6,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 27,38</t>
+          <t>-42,94; 28,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 25,93</t>
+          <t>-47,73; 20,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; -20,23</t>
+          <t>-64,9; -14,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 34,89</t>
+          <t>-25,92; 35,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,21; -1,26</t>
+          <t>-50,14; -2,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,62; -21,99</t>
+          <t>-59,55; -22,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,62</t>
+          <t>-3,71; 5,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,01</t>
+          <t>-7,65; 1,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -2,84</t>
+          <t>-12,87; -3,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 7,91</t>
+          <t>-1,61; 7,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,9</t>
+          <t>-7,21; 0,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -2,53</t>
+          <t>-9,65; -2,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,2</t>
+          <t>-1,23; 5,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,25</t>
+          <t>-5,88; 0,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -4,05</t>
+          <t>-10,12; -3,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 52,91</t>
+          <t>-24,03; 55,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 10,92</t>
+          <t>-47,8; 12,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -26,52</t>
+          <t>-82,44; -28,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 78,35</t>
+          <t>-11,37; 73,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 9,11</t>
+          <t>-49,81; 6,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,67; -24,05</t>
+          <t>-63,35; -24,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 45,91</t>
+          <t>-8,82; 47,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -2,34</t>
+          <t>-41,29; 0,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,42; -36,22</t>
+          <t>-71,89; -34,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 7,73</t>
+          <t>-7,11; 7,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -2,02</t>
+          <t>-15,69; -2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -9,43</t>
+          <t>-20,05; -8,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 5,83</t>
+          <t>-6,61; 6,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -0,82</t>
+          <t>-13,16; -0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -9,43</t>
+          <t>-19,51; -9,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,0</t>
+          <t>-4,88; 4,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -2,97</t>
+          <t>-12,56; -3,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -10,46</t>
+          <t>-18,6; -10,79</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 37,97</t>
+          <t>-23,86; 31,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -8,43</t>
+          <t>-51,86; -9,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,07; -42,24</t>
+          <t>-66,86; -39,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 28,52</t>
+          <t>-23,43; 30,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,2; -3,35</t>
+          <t>-47,19; -4,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,9; -47,73</t>
+          <t>-69,86; -47,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 22,04</t>
+          <t>-17,68; 18,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -13,12</t>
+          <t>-46,02; -14,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,68; -48,25</t>
+          <t>-65,7; -48,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 10,05</t>
+          <t>-8,15; 10,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-22,12; -4,4</t>
+          <t>-22,94; -5,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -13,28</t>
+          <t>-27,76; -13,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 9,05</t>
+          <t>-7,53; 8,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -5,91</t>
+          <t>-22,06; -5,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -17,04</t>
+          <t>-40,83; -15,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 6,61</t>
+          <t>-5,3; 7,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -7,53</t>
+          <t>-19,61; -7,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-35,05; -17,75</t>
+          <t>-34,06; -17,32</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 30,64</t>
+          <t>-18,61; 30,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,53; -13,06</t>
+          <t>-52,71; -13,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,49; -38,96</t>
+          <t>-62,55; -39,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 24,35</t>
+          <t>-16,84; 24,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -15,71</t>
+          <t>-48,13; -15,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-86,78; -41,67</t>
+          <t>-85,62; -39,77</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 17,83</t>
+          <t>-12,17; 19,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-45,8; -19,92</t>
+          <t>-45,4; -19,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,63; -45,53</t>
+          <t>-78,72; -44,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 6,01</t>
+          <t>-17,07; 6,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,89; -3,25</t>
+          <t>-24,85; -2,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -4,3</t>
+          <t>-23,28; -3,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 3,16</t>
+          <t>-14,84; 3,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-39,14; -20,01</t>
+          <t>-39,87; -19,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-29,01; -13,23</t>
+          <t>-28,49; -13,3</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 1,88</t>
+          <t>-12,05; 2,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-31,15; -15,77</t>
+          <t>-30,79; -15,65</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-24,21; -12,04</t>
+          <t>-24,53; -11,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 13,76</t>
+          <t>-30,95; 15,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-44,37; -7,19</t>
+          <t>-44,73; -5,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,94; -10,59</t>
+          <t>-41,45; -7,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 5,83</t>
+          <t>-22,36; 6,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,46; -35,25</t>
+          <t>-61,35; -34,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-43,51; -24,4</t>
+          <t>-42,92; -24,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 3,86</t>
+          <t>-19,78; 5,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,0; -29,66</t>
+          <t>-51,5; -29,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -23,23</t>
+          <t>-39,93; -23,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,33</t>
+          <t>-0,56; 3,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -1,13</t>
+          <t>-4,66; -1,24</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -2,15</t>
+          <t>-6,82; -2,38</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,98</t>
+          <t>0,12; 4,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -2,58</t>
+          <t>-6,38; -2,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -3,12</t>
+          <t>-7,37; -3,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,25</t>
+          <t>0,34; 3,1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -2,46</t>
+          <t>-5,13; -2,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -3,25</t>
+          <t>-6,17; -3,27</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 26,18</t>
+          <t>-3,9; 24,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -8,87</t>
+          <t>-32,58; -9,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -17,27</t>
+          <t>-46,88; -18,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,86; 26,31</t>
+          <t>0,72; 27,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-36,72; -16,71</t>
+          <t>-37,63; -17,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -20,92</t>
+          <t>-44,52; -21,06</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,8; 22,8</t>
+          <t>2,17; 21,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -16,88</t>
+          <t>-32,71; -16,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -22,72</t>
+          <t>-40,68; -22,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C05-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,29</t>
+          <t>-2,8; 2,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,53</t>
+          <t>-2,07; 3,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,7</t>
+          <t>-3,41; 3,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,75</t>
+          <t>-0,38; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,14</t>
+          <t>-1,12; 3,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,1</t>
+          <t>-2,27; 3,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,57</t>
+          <t>-0,87; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,49</t>
+          <t>-0,87; 2,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,99</t>
+          <t>-2,32; 1,72</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-56,56%</t>
+          <t>-32,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-40,63%</t>
+          <t>-13,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-49,69%</t>
+          <t>-24,41%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 126,25</t>
+          <t>-62,24; 107,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 167,35</t>
+          <t>-50,5; 189,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,3; 123,27</t>
+          <t>-91,51; 157,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 417,98</t>
+          <t>-18,81; 387,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 256,5</t>
+          <t>-42,93; 300,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-98,01; 231,72</t>
+          <t>-96,89; 270,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 131,31</t>
+          <t>-24,71; 140,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 124,19</t>
+          <t>-29,83; 142,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 60,99</t>
+          <t>-74,22; 98,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,32</t>
+          <t>-2,02; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,67</t>
+          <t>-1,36; 3,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,13</t>
+          <t>-1,57; 4,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,25</t>
+          <t>-0,38; 5,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,9</t>
+          <t>-2,53; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,58</t>
+          <t>-2,33; 2,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,89</t>
+          <t>-0,44; 2,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,09</t>
+          <t>-1,34; 2,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,53</t>
+          <t>-1,09; 2,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,55%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 105,63</t>
+          <t>-45,02; 116,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 164,59</t>
+          <t>-34,66; 161,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 171,98</t>
+          <t>-38,96; 228,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 186,6</t>
+          <t>-16,36; 193,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 72,93</t>
+          <t>-51,09; 74,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 90,3</t>
+          <t>-47,86; 104,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 111,2</t>
+          <t>-11,23; 104,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 78,99</t>
+          <t>-31,49; 68,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 83,3</t>
+          <t>-27,52; 105,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-3,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 4,55</t>
+          <t>-1,84; 4,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,61</t>
+          <t>-5,27; 0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,12</t>
+          <t>-5,65; 0,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,83</t>
+          <t>-4,02; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,28</t>
+          <t>-4,53; 1,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -1,05</t>
+          <t>-6,53; -1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,26</t>
+          <t>-2,24; 2,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,2</t>
+          <t>-4,36; -0,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -1,54</t>
+          <t>-5,3; -1,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-41,41%</t>
+          <t>-42,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,13%</t>
+          <t>-44,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-44,01%</t>
+          <t>-44,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 87,31</t>
+          <t>-23,59; 88,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 14,37</t>
+          <t>-63,88; 7,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 6,21</t>
+          <t>-65,97; 3,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 28,73</t>
+          <t>-40,16; 31,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 20,0</t>
+          <t>-46,65; 19,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,9; -14,18</t>
+          <t>-62,68; -11,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 35,49</t>
+          <t>-25,66; 34,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,14; -2,78</t>
+          <t>-48,21; -2,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,55; -22,09</t>
+          <t>-60,29; -23,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,38</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,03</t>
+          <t>-5,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,74</t>
+          <t>-5,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,75</t>
+          <t>-3,85; 5,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,15</t>
+          <t>-7,84; 1,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -3,19</t>
+          <t>-9,8; -1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,45</t>
+          <t>-1,28; 7,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 0,62</t>
+          <t>-7,36; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -2,62</t>
+          <t>-9,49; -2,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,27</t>
+          <t>-1,59; 5,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 0,06</t>
+          <t>-6,25; -0,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -3,8</t>
+          <t>-8,44; -3,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-56,46%</t>
+          <t>-41,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,73%</t>
+          <t>-45,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,5%</t>
+          <t>-43,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 55,74</t>
+          <t>-25,58; 52,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 12,9</t>
+          <t>-48,39; 11,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,44; -28,07</t>
+          <t>-60,49; -11,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 73,68</t>
+          <t>-8,62; 76,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 6,1</t>
+          <t>-48,93; 5,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,35; -24,54</t>
+          <t>-61,07; -24,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 47,87</t>
+          <t>-10,66; 46,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 0,99</t>
+          <t>-42,63; -3,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,89; -34,73</t>
+          <t>-56,09; -27,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-14,6</t>
+          <t>-14,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-14,69</t>
+          <t>-14,07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,56</t>
+          <t>-14,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 7,31</t>
+          <t>-6,85; 7,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,69; -2,44</t>
+          <t>-16,15; -2,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -8,86</t>
+          <t>-20,06; -8,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 6,36</t>
+          <t>-6,33; 6,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -0,95</t>
+          <t>-13,3; -0,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,51; -9,6</t>
+          <t>-19,77; -9,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,31</t>
+          <t>-4,53; 5,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -3,41</t>
+          <t>-12,2; -3,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -10,79</t>
+          <t>-18,18; -10,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-55,89%</t>
+          <t>-54,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-60,64%</t>
+          <t>-58,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-58,01%</t>
+          <t>-56,2%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 31,82</t>
+          <t>-23,49; 35,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-51,86; -9,62</t>
+          <t>-52,84; -10,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,86; -39,95</t>
+          <t>-65,89; -38,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 30,39</t>
+          <t>-22,84; 35,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,19; -4,17</t>
+          <t>-47,48; -3,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,86; -47,39</t>
+          <t>-68,11; -45,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 18,93</t>
+          <t>-16,99; 23,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,02; -14,98</t>
+          <t>-44,32; -15,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -48,59</t>
+          <t>-64,72; -47,17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-20,29</t>
+          <t>-20,82</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-26,49</t>
+          <t>-18,76</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-23,92</t>
+          <t>-19,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,11</t>
+          <t>-7,71; 10,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-22,94; -5,1</t>
+          <t>-22,6; -4,02</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-27,76; -13,62</t>
+          <t>-27,53; -13,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 8,97</t>
+          <t>-7,79; 8,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -5,92</t>
+          <t>-21,55; -5,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-40,83; -15,55</t>
+          <t>-25,18; -11,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,3</t>
+          <t>-5,01; 6,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -7,68</t>
+          <t>-20,08; -7,99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-34,06; -17,32</t>
+          <t>-24,71; -15,19</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-52,19%</t>
+          <t>-53,54%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-63,46%</t>
+          <t>-44,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-59,18%</t>
+          <t>-48,99%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 30,5</t>
+          <t>-18,34; 32,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,71; -13,64</t>
+          <t>-53,41; -12,77</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -39,02</t>
+          <t>-63,08; -40,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 24,91</t>
+          <t>-17,32; 23,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -15,34</t>
+          <t>-48,26; -15,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,62; -39,77</t>
+          <t>-53,88; -32,1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 19,75</t>
+          <t>-11,37; 18,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-45,4; -19,93</t>
+          <t>-46,37; -21,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,72; -44,68</t>
+          <t>-55,91; -41,11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-13,5</t>
+          <t>-13,78</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-21,12</t>
+          <t>-21,82</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-18,33</t>
+          <t>-18,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 6,53</t>
+          <t>-15,34; 7,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -2,28</t>
+          <t>-25,3; -2,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-23,28; -3,17</t>
+          <t>-24,26; -3,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,57</t>
+          <t>-15,31; 3,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -19,97</t>
+          <t>-39,63; -19,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -13,3</t>
+          <t>-28,8; -13,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 2,79</t>
+          <t>-12,42; 1,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,79; -15,65</t>
+          <t>-30,72; -16,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-24,53; -11,79</t>
+          <t>-24,91; -12,74</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-27,38%</t>
+          <t>-27,93%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-34,66%</t>
+          <t>-35,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-32,42%</t>
+          <t>-33,37%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 15,38</t>
+          <t>-28,1; 16,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-44,73; -5,02</t>
+          <t>-45,59; -6,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,45; -7,81</t>
+          <t>-42,23; -8,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 6,17</t>
+          <t>-23,0; 6,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -34,68</t>
+          <t>-60,98; -34,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,92; -24,35</t>
+          <t>-43,93; -25,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 5,53</t>
+          <t>-20,38; 3,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-51,5; -29,88</t>
+          <t>-51,96; -30,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,93; -23,11</t>
+          <t>-40,98; -24,58</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,07</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-3,69</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,1</t>
+          <t>-0,31; 3,38</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,24</t>
+          <t>-4,65; -1,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -2,38</t>
+          <t>-5,04; -1,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,18</t>
+          <t>-0,07; 3,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -2,67</t>
+          <t>-6,26; -2,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -3,15</t>
+          <t>-5,67; -2,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,1</t>
+          <t>0,34; 3,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -2,42</t>
+          <t>-5,15; -2,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -3,27</t>
+          <t>-4,86; -2,36</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-23,71%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-31,08%</t>
+          <t>-25,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>-24,69%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 24,38</t>
+          <t>-2,47; 26,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -9,71</t>
+          <t>-32,01; -8,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-46,88; -18,62</t>
+          <t>-33,48; -10,89</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,72; 27,54</t>
+          <t>-0,54; 26,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,63; -17,64</t>
+          <t>-37,33; -17,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-44,52; -21,06</t>
+          <t>-33,01; -16,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,17; 21,78</t>
+          <t>2,06; 22,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-32,71; -16,9</t>
+          <t>-32,3; -16,15</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -22,82</t>
+          <t>-31,14; -17,03</t>
         </is>
       </c>
     </row>
